--- a/real_estate_feedback_forms/027_tenant_satisfaction_survey--real_estate_feedback_forms.xlsx
+++ b/real_estate_feedback_forms/027_tenant_satisfaction_survey--real_estate_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'laundry_facilities',_'label':_'laundry_facilities'}</t>
+          <t>laundry_facilities</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'laundry_facilities', 'label': 'Laundry Facilities'}</t>
+          <t>Laundry Facilities</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'parking',_'label':_'parking'}</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'parking', 'label': 'Parking'}</t>
+          <t>Parking</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'pool_table',_'label':_'pool_table'}</t>
+          <t>pool_table</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'pool_table', 'label': 'Pool Table'}</t>
+          <t>Pool Table</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'game_room',_'label':_'game_room'}</t>
+          <t>game_room</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'game_room', 'label': 'Game Room'}</t>
+          <t>Game Room</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'exercise_room',_'label':_'exercise_room'}</t>
+          <t>exercise_room</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'exercise_room', 'label': 'Exercise Room'}</t>
+          <t>Exercise Room</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'movie_theater',_'label':_'movie_theater'}</t>
+          <t>movie_theater</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'movie_theater', 'label': 'Movie Theater'}</t>
+          <t>Movie Theater</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'gym',_'label':_'gym'}</t>
+          <t>gym</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'gym', 'label': 'Gym'}</t>
+          <t>Gym</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'community_room',_'label':_'community_room'}</t>
+          <t>community_room</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'community_room', 'label': 'Community Room'}</t>
+          <t>Community Room</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'game_room',_'label':_'game_room'}</t>
+          <t>parking_lot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'game_room', 'label': 'Game Room'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>amenities_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'value':_'parking_lot',_'label':_'parking_lot'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'value': 'parking_lot', 'label': 'Parking Lot'}</t>
+          <t>Parking Lot</t>
         </is>
       </c>
     </row>
